--- a/exports/trend_1d/BEL_full_report.xlsx
+++ b/exports/trend_1d/BEL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>15.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42072</v>
+        <v>42073</v>
       </c>
       <c r="H2" t="n">
-        <v>34.8</v>
+        <v>33.5</v>
       </c>
       <c r="I2" t="n">
         <v>33.84339022493211</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>1.36</v>
       </c>
       <c r="L2" t="n">
         <v>4.24</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>17.54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42095</v>
+        <v>42100</v>
       </c>
       <c r="H3" t="n">
-        <v>35.3</v>
+        <v>36.3</v>
       </c>
       <c r="I3" t="n">
         <v>35.35466678801385</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.37</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>8.359999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="M3" t="n">
         <v>2.24</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>12.32</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42110</v>
+        <v>42111</v>
       </c>
       <c r="H4" t="n">
-        <v>33.3</v>
+        <v>32.4</v>
       </c>
       <c r="I4" t="n">
         <v>33.27778345226001</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.26</v>
+        <v>-10.74</v>
       </c>
       <c r="L4" t="n">
-        <v>8.68</v>
+        <v>11.02</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>15.07</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H5" t="n">
-        <v>33.7</v>
+        <v>36.15</v>
       </c>
       <c r="I5" t="n">
         <v>33.84198091521799</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.01</v>
+        <v>-11.57</v>
       </c>
       <c r="L5" t="n">
-        <v>5.09</v>
+        <v>13.12</v>
       </c>
       <c r="M5" t="n">
         <v>1.48</v>
       </c>
       <c r="N5" t="n">
-        <v>4.42</v>
+        <v>7.27</v>
       </c>
       <c r="O5" t="n">
         <v>-2.7</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.53</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42165</v>
+        <v>42166</v>
       </c>
       <c r="H6" t="n">
-        <v>33.05</v>
+        <v>32.4</v>
       </c>
       <c r="I6" t="n">
         <v>32.66157111835016</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>-8.58</v>
+        <v>-10.37</v>
       </c>
       <c r="L6" t="n">
         <v>11.62</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>13.61</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42200</v>
+        <v>42201</v>
       </c>
       <c r="H7" t="n">
-        <v>35.6</v>
+        <v>36.95</v>
       </c>
       <c r="I7" t="n">
         <v>36.29039921667186</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.880000000000001</v>
+        <v>-14.04</v>
       </c>
       <c r="L7" t="n">
-        <v>10.65</v>
+        <v>14.66</v>
       </c>
       <c r="M7" t="n">
         <v>0.76</v>
       </c>
       <c r="N7" t="n">
-        <v>2.2</v>
+        <v>3.79</v>
       </c>
       <c r="O7" t="n">
         <v>-1.97</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.48</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42227</v>
+        <v>42228</v>
       </c>
       <c r="H8" t="n">
-        <v>38.5</v>
+        <v>37.65</v>
       </c>
       <c r="I8" t="n">
         <v>37.95254831600585</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K8" t="n">
-        <v>4.19</v>
+        <v>1.89</v>
       </c>
       <c r="L8" t="n">
         <v>3.79</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>10.77</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42285</v>
+        <v>42286</v>
       </c>
       <c r="H9" t="n">
-        <v>36.45</v>
+        <v>36.6</v>
       </c>
       <c r="I9" t="n">
         <v>36.54407475990332</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>3.19</v>
+        <v>2.79</v>
       </c>
       <c r="L9" t="n">
         <v>3.72</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.58</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42348</v>
+        <v>42349</v>
       </c>
       <c r="H10" t="n">
-        <v>36.1</v>
+        <v>35.5</v>
       </c>
       <c r="I10" t="n">
         <v>35.78527828633555</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.37</v>
+        <v>-3.01</v>
       </c>
       <c r="L10" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="M10" t="n">
         <v>1.19</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42361</v>
+        <v>42362</v>
       </c>
       <c r="H11" t="n">
-        <v>38.55</v>
+        <v>39.9</v>
       </c>
       <c r="I11" t="n">
         <v>38.73669308880775</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.59</v>
+        <v>-12.39</v>
       </c>
       <c r="L11" t="n">
-        <v>9.44</v>
+        <v>13.94</v>
       </c>
       <c r="M11" t="n">
         <v>1.26</v>
       </c>
       <c r="N11" t="n">
-        <v>2.47</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
         <v>-1.66</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H12" t="n">
-        <v>39.6</v>
+        <v>38.15</v>
       </c>
       <c r="I12" t="n">
         <v>38.95306738858618</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.75</v>
+        <v>-4.39</v>
       </c>
       <c r="L12" t="n">
-        <v>3.51</v>
+        <v>5.64</v>
       </c>
       <c r="M12" t="n">
         <v>1.35</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>13.31</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42447</v>
+        <v>42450</v>
       </c>
       <c r="H13" t="n">
-        <v>33.4</v>
+        <v>35.65</v>
       </c>
       <c r="I13" t="n">
         <v>35.25224244135997</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K13" t="n">
-        <v>12.45</v>
+        <v>6.55</v>
       </c>
       <c r="L13" t="n">
         <v>5.24</v>
@@ -1182,7 +1337,7 @@
         <v>1.62</v>
       </c>
       <c r="N13" t="n">
-        <v>3.23</v>
+        <v>6.74</v>
       </c>
       <c r="O13" t="n">
         <v>-3.66</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>12.68</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42509</v>
+        <v>42510</v>
       </c>
       <c r="H14" t="n">
-        <v>33.85</v>
+        <v>33.35</v>
       </c>
       <c r="I14" t="n">
         <v>33.52826553708552</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.05</v>
+        <v>-6.45</v>
       </c>
       <c r="L14" t="n">
-        <v>6.31</v>
+        <v>6.87</v>
       </c>
       <c r="M14" t="n">
         <v>1.55</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H15" t="n">
-        <v>35.85</v>
+        <v>36.1</v>
       </c>
       <c r="I15" t="n">
         <v>36.02571795507092</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.5</v>
+        <v>-8.25</v>
       </c>
       <c r="L15" t="n">
         <v>9.449999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="N15" t="n">
         <v>5.29</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.08</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42726</v>
+        <v>42727</v>
       </c>
       <c r="H16" t="n">
-        <v>42.25</v>
+        <v>41.95</v>
       </c>
       <c r="I16" t="n">
         <v>42.07237061294235</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K16" t="n">
-        <v>17.04</v>
+        <v>16.2</v>
       </c>
       <c r="L16" t="n">
         <v>4.29</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>9.369999999999999</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42744</v>
+        <v>42745</v>
       </c>
       <c r="H17" t="n">
-        <v>44.05</v>
+        <v>45.8</v>
       </c>
       <c r="I17" t="n">
         <v>44.91812909434174</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.01</v>
+        <v>-9.18</v>
       </c>
       <c r="L17" t="n">
-        <v>8.699999999999999</v>
+        <v>10.37</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
         <v>4.11</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.46</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42878</v>
+        <v>42879</v>
       </c>
       <c r="H18" t="n">
-        <v>52.15</v>
+        <v>50.55</v>
       </c>
       <c r="I18" t="n">
         <v>51.71336937505261</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K18" t="n">
-        <v>13.86</v>
+        <v>10.37</v>
       </c>
       <c r="L18" t="n">
         <v>3.71</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.97</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42923</v>
+        <v>42926</v>
       </c>
       <c r="H19" t="n">
-        <v>51.55</v>
+        <v>52.35</v>
       </c>
       <c r="I19" t="n">
         <v>52.33842704216835</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.98</v>
+        <v>-3.56</v>
       </c>
       <c r="L19" t="n">
         <v>6.03</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.33</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H20" t="n">
-        <v>54.3</v>
+        <v>51.75</v>
       </c>
       <c r="I20" t="n">
         <v>51.9280793702841</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K20" t="n">
-        <v>3.72</v>
+        <v>-1.15</v>
       </c>
       <c r="L20" t="n">
         <v>3.72</v>
@@ -1581,7 +1820,7 @@
         <v>0.64</v>
       </c>
       <c r="N20" t="n">
-        <v>1.45</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.55</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42963</v>
+        <v>42964</v>
       </c>
       <c r="H21" t="n">
-        <v>53.1</v>
+        <v>55.5</v>
       </c>
       <c r="I21" t="n">
         <v>55.08754494131524</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.61</v>
+        <v>-7.25</v>
       </c>
       <c r="L21" t="n">
-        <v>4.44</v>
+        <v>8.31</v>
       </c>
       <c r="M21" t="n">
         <v>0.68</v>
       </c>
       <c r="N21" t="n">
-        <v>2.99</v>
+        <v>4.52</v>
       </c>
       <c r="O21" t="n">
         <v>-4.7</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.09</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H22" t="n">
-        <v>55.3</v>
+        <v>53.6</v>
       </c>
       <c r="I22" t="n">
         <v>54.72421639623779</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.36</v>
+        <v>-3.42</v>
       </c>
       <c r="L22" t="n">
         <v>4.95</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>11.55</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43038</v>
+        <v>43039</v>
       </c>
       <c r="H23" t="n">
-        <v>58.5</v>
+        <v>61.55</v>
       </c>
       <c r="I23" t="n">
         <v>59.22626964784293</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K23" t="n">
-        <v>-9.140000000000001</v>
+        <v>-14.83</v>
       </c>
       <c r="L23" t="n">
-        <v>9.98</v>
+        <v>19.68</v>
       </c>
       <c r="M23" t="n">
-        <v>3.26</v>
+        <v>5.98</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>5.21</v>
       </c>
       <c r="O23" t="n">
         <v>-3.07</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>7.55</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H24" t="n">
-        <v>59.55</v>
+        <v>57.75</v>
       </c>
       <c r="I24" t="n">
         <v>58.3905909926582</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.25</v>
+        <v>-6.17</v>
       </c>
       <c r="L24" t="n">
         <v>6.82</v>
@@ -1809,7 +2096,7 @@
         <v>0.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.28</v>
+        <v>3.02</v>
       </c>
       <c r="O24" t="n">
         <v>5.21</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.93</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43311</v>
+        <v>43312</v>
       </c>
       <c r="H25" t="n">
-        <v>35.95</v>
+        <v>38.8</v>
       </c>
       <c r="I25" t="n">
         <v>37.91812952210761</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K25" t="n">
-        <v>37.75</v>
+        <v>32.81</v>
       </c>
       <c r="L25" t="n">
         <v>3.64</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>17.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H26" t="n">
-        <v>36.4</v>
+        <v>31.5</v>
       </c>
       <c r="I26" t="n">
         <v>35.73888176663343</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.19</v>
+        <v>-18.81</v>
       </c>
       <c r="L26" t="n">
-        <v>7.86</v>
+        <v>23.07</v>
       </c>
       <c r="M26" t="n">
         <v>0.63</v>
       </c>
       <c r="N26" t="n">
-        <v>3.22</v>
+        <v>13.46</v>
       </c>
       <c r="O26" t="n">
         <v>7.93</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>22.15</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43402</v>
+        <v>43403</v>
       </c>
       <c r="H27" t="n">
-        <v>28.8</v>
+        <v>29.95</v>
       </c>
       <c r="I27" t="n">
         <v>29.81589519740572</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K27" t="n">
-        <v>8.57</v>
+        <v>4.92</v>
       </c>
       <c r="L27" t="n">
         <v>15.71</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>16.79</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43433</v>
+        <v>43434</v>
       </c>
       <c r="H28" t="n">
-        <v>28.25</v>
+        <v>27.75</v>
       </c>
       <c r="I28" t="n">
         <v>28.10679320883561</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.68</v>
+        <v>-7.35</v>
       </c>
       <c r="L28" t="n">
-        <v>7.01</v>
+        <v>7.85</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>14.78</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43453</v>
+        <v>43454</v>
       </c>
       <c r="H29" t="n">
-        <v>28.9</v>
+        <v>30.1</v>
       </c>
       <c r="I29" t="n">
         <v>29.38388817365012</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.14</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>4.86</v>
+        <v>9.19</v>
       </c>
       <c r="M29" t="n">
         <v>1.12</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>14.15</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43487</v>
+        <v>43488</v>
       </c>
       <c r="H30" t="n">
-        <v>28.4</v>
+        <v>27.95</v>
       </c>
       <c r="I30" t="n">
         <v>28.03640441462927</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.65</v>
+        <v>-7.14</v>
       </c>
       <c r="L30" t="n">
-        <v>6.64</v>
+        <v>7.48</v>
       </c>
       <c r="M30" t="n">
         <v>1.71</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.31</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43524</v>
+        <v>43525</v>
       </c>
       <c r="H31" t="n">
-        <v>27.5</v>
+        <v>28.35</v>
       </c>
       <c r="I31" t="n">
         <v>28.22259732773195</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K31" t="n">
-        <v>1.61</v>
+        <v>-1.43</v>
       </c>
       <c r="L31" t="n">
         <v>5.01</v>
@@ -2208,7 +2579,7 @@
         <v>4.29</v>
       </c>
       <c r="N31" t="n">
-        <v>2.86</v>
+        <v>3.09</v>
       </c>
       <c r="O31" t="n">
         <v>-1.58</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.52</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43579</v>
+        <v>43580</v>
       </c>
       <c r="H32" t="n">
-        <v>29.45</v>
+        <v>29</v>
       </c>
       <c r="I32" t="n">
         <v>29.35342929202249</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.88</v>
+        <v>2.29</v>
       </c>
       <c r="L32" t="n">
         <v>2.47</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.77</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H33" t="n">
-        <v>30.65</v>
+        <v>33.1</v>
       </c>
       <c r="I33" t="n">
         <v>31.28328088796584</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.69</v>
+        <v>-14.14</v>
       </c>
       <c r="L33" t="n">
-        <v>6.21</v>
+        <v>15</v>
       </c>
       <c r="M33" t="n">
-        <v>0.85</v>
+        <v>3.43</v>
       </c>
       <c r="N33" t="n">
-        <v>3.63</v>
+        <v>7.99</v>
       </c>
       <c r="O33" t="n">
         <v>-1.53</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.93</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43651</v>
+        <v>43654</v>
       </c>
       <c r="H34" t="n">
-        <v>36.15</v>
+        <v>33.75</v>
       </c>
       <c r="I34" t="n">
         <v>35.01323475890023</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K34" t="n">
-        <v>9.210000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="L34" t="n">
         <v>4.23</v>
@@ -2379,7 +2786,7 @@
         <v>0.41</v>
       </c>
       <c r="N34" t="n">
-        <v>5.57</v>
+        <v>6.64</v>
       </c>
       <c r="O34" t="n">
         <v>7.99</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>16.86</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43711</v>
+        <v>43712</v>
       </c>
       <c r="H35" t="n">
-        <v>33.6</v>
+        <v>35.5</v>
       </c>
       <c r="I35" t="n">
         <v>35.13439263262494</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K35" t="n">
-        <v>0.44</v>
+        <v>-5.19</v>
       </c>
       <c r="L35" t="n">
         <v>8.44</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>14.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43774</v>
+        <v>43775</v>
       </c>
       <c r="H36" t="n">
-        <v>37.55</v>
+        <v>36.45</v>
       </c>
       <c r="I36" t="n">
         <v>36.74916069172377</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K36" t="n">
-        <v>5.77</v>
+        <v>2.68</v>
       </c>
       <c r="L36" t="n">
         <v>5.21</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>11.76</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43845</v>
+        <v>43846</v>
       </c>
       <c r="H37" t="n">
-        <v>34.6</v>
+        <v>35.25</v>
       </c>
       <c r="I37" t="n">
         <v>34.77052608898882</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K37" t="n">
-        <v>5.08</v>
+        <v>3.29</v>
       </c>
       <c r="L37" t="n">
         <v>3.16</v>
       </c>
       <c r="M37" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="N37" t="n">
         <v>3.9</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43860</v>
+        <v>43861</v>
       </c>
       <c r="H38" t="n">
-        <v>33.6</v>
+        <v>30.2</v>
       </c>
       <c r="I38" t="n">
         <v>32.60916223526752</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.68</v>
+        <v>-14.33</v>
       </c>
       <c r="L38" t="n">
-        <v>5.96</v>
+        <v>15.04</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>4.46</v>
       </c>
       <c r="N38" t="n">
-        <v>3.86</v>
+        <v>10.12</v>
       </c>
       <c r="O38" t="n">
         <v>1.88</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>16.83</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43942</v>
+        <v>43943</v>
       </c>
       <c r="H39" t="n">
-        <v>25.3</v>
+        <v>25.55</v>
       </c>
       <c r="I39" t="n">
         <v>25.42000725567286</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K39" t="n">
-        <v>16.23</v>
+        <v>15.4</v>
       </c>
       <c r="L39" t="n">
         <v>9.27</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>19.89</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43957</v>
+        <v>43958</v>
       </c>
       <c r="H40" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="I40" t="n">
         <v>21.00953258018872</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>-17.03</v>
+        <v>-18.2</v>
       </c>
       <c r="L40" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="M40" t="n">
         <v>2.29</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>18.87</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>43984</v>
+        <v>43985</v>
       </c>
       <c r="H41" t="n">
-        <v>23.2</v>
+        <v>24.55</v>
       </c>
       <c r="I41" t="n">
         <v>23.43313160500078</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>-11</v>
+        <v>-17.46</v>
       </c>
       <c r="L41" t="n">
-        <v>14.59</v>
+        <v>18.42</v>
       </c>
       <c r="M41" t="n">
         <v>6.19</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>16.28</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H42" t="n">
-        <v>34.65</v>
+        <v>32.1</v>
       </c>
       <c r="I42" t="n">
         <v>33.32307607704384</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K42" t="n">
-        <v>41.14</v>
+        <v>30.75</v>
       </c>
       <c r="L42" t="n">
         <v>8.550000000000001</v>
@@ -2835,7 +3338,7 @@
         <v>4.67</v>
       </c>
       <c r="N42" t="n">
-        <v>5.35</v>
+        <v>7.36</v>
       </c>
       <c r="O42" t="n">
         <v>5.82</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>16.42</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44147</v>
+        <v>44148</v>
       </c>
       <c r="H43" t="n">
-        <v>31.4</v>
+        <v>32.25</v>
       </c>
       <c r="I43" t="n">
         <v>32.1556197505705</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K43" t="n">
-        <v>2.18</v>
+        <v>-0.47</v>
       </c>
       <c r="L43" t="n">
         <v>7.79</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>11.46</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44271</v>
+        <v>44272</v>
       </c>
       <c r="H44" t="n">
-        <v>45.95</v>
+        <v>44.6</v>
       </c>
       <c r="I44" t="n">
         <v>44.84168781215139</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K44" t="n">
-        <v>42.48</v>
+        <v>38.29</v>
       </c>
       <c r="L44" t="n">
         <v>4.19</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>14.5</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44320</v>
+        <v>44321</v>
       </c>
       <c r="H45" t="n">
-        <v>44.25</v>
+        <v>45.95</v>
       </c>
       <c r="I45" t="n">
         <v>45.56388408943637</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K45" t="n">
-        <v>0.78</v>
+        <v>-3.03</v>
       </c>
       <c r="L45" t="n">
         <v>3.48</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>12.16</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44414</v>
+        <v>44417</v>
       </c>
       <c r="H46" t="n">
-        <v>58.45</v>
+        <v>57.05</v>
       </c>
       <c r="I46" t="n">
         <v>58.13518134638179</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K46" t="n">
-        <v>27.2</v>
+        <v>24.16</v>
       </c>
       <c r="L46" t="n">
         <v>3.92</v>
       </c>
       <c r="M46" t="n">
-        <v>2.87</v>
+        <v>5.9</v>
       </c>
       <c r="N46" t="n">
         <v>4.88</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H47" t="n">
-        <v>61.35</v>
+        <v>62.2</v>
       </c>
       <c r="I47" t="n">
         <v>61.97769305858776</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
-        <v>-7.54</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>9.109999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M47" t="n">
         <v>0.79</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.26</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H48" t="n">
-        <v>70.55</v>
+        <v>66.05</v>
       </c>
       <c r="I48" t="n">
         <v>66.97411222734904</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K48" t="n">
-        <v>13.42</v>
+        <v>6.19</v>
       </c>
       <c r="L48" t="n">
         <v>1.69</v>
@@ -3177,7 +3752,7 @@
         <v>2.56</v>
       </c>
       <c r="N48" t="n">
-        <v>4.77</v>
+        <v>6.38</v>
       </c>
       <c r="O48" t="n">
         <v>1.39</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>15.39</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44564</v>
+        <v>44565</v>
       </c>
       <c r="H49" t="n">
-        <v>70.40000000000001</v>
+        <v>72.05</v>
       </c>
       <c r="I49" t="n">
         <v>71.99266089579324</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>-6.59</v>
+        <v>-9.08</v>
       </c>
       <c r="L49" t="n">
-        <v>8.33</v>
+        <v>10.52</v>
       </c>
       <c r="M49" t="n">
         <v>0.87</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>8.65</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H50" t="n">
-        <v>69</v>
+        <v>65.75</v>
       </c>
       <c r="I50" t="n">
         <v>67.16078834157796</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.23</v>
+        <v>-8.74</v>
       </c>
       <c r="L50" t="n">
-        <v>5.14</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="M50" t="n">
         <v>1.05</v>
       </c>
       <c r="N50" t="n">
-        <v>3.74</v>
+        <v>4.71</v>
       </c>
       <c r="O50" t="n">
         <v>2.34</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>13.15</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44620</v>
+        <v>44622</v>
       </c>
       <c r="H51" t="n">
-        <v>70.15000000000001</v>
+        <v>72</v>
       </c>
       <c r="I51" t="n">
         <v>70.26622275863797</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.69</v>
+        <v>-9.51</v>
       </c>
       <c r="L51" t="n">
         <v>11.41</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>12.56</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H52" t="n">
-        <v>79.40000000000001</v>
+        <v>77.05</v>
       </c>
       <c r="I52" t="n">
         <v>77.23421804590822</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K52" t="n">
-        <v>10.28</v>
+        <v>7.01</v>
       </c>
       <c r="L52" t="n">
         <v>5.9</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>12.09</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44712</v>
+        <v>44713</v>
       </c>
       <c r="H53" t="n">
-        <v>78.25</v>
+        <v>82.05</v>
       </c>
       <c r="I53" t="n">
         <v>81.1627735830715</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.56</v>
+        <v>-6.49</v>
       </c>
       <c r="L53" t="n">
-        <v>3.89</v>
+        <v>7.14</v>
       </c>
       <c r="M53" t="n">
         <v>1.73</v>
       </c>
       <c r="N53" t="n">
-        <v>3.7</v>
+        <v>4.86</v>
       </c>
       <c r="O53" t="n">
         <v>-2.96</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>12.63</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H54" t="n">
-        <v>106.65</v>
+        <v>100.7</v>
       </c>
       <c r="I54" t="n">
         <v>104.6566284541154</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K54" t="n">
-        <v>29.98</v>
+        <v>22.73</v>
       </c>
       <c r="L54" t="n">
         <v>9.140000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="N54" t="n">
-        <v>4.56</v>
+        <v>5.58</v>
       </c>
       <c r="O54" t="n">
         <v>4.86</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>12.65</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44867</v>
+        <v>44868</v>
       </c>
       <c r="H55" t="n">
-        <v>107.1</v>
+        <v>109.95</v>
       </c>
       <c r="I55" t="n">
         <v>109.6181063244964</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.36</v>
+        <v>-9.19</v>
       </c>
       <c r="L55" t="n">
-        <v>9.630000000000001</v>
+        <v>11.42</v>
       </c>
       <c r="M55" t="n">
         <v>1.83</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>10.51</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44910</v>
+        <v>44911</v>
       </c>
       <c r="H56" t="n">
-        <v>103.25</v>
+        <v>99.45</v>
       </c>
       <c r="I56" t="n">
         <v>100.6488388122207</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.09</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>6.55</v>
+        <v>11.01</v>
       </c>
       <c r="M56" t="n">
-        <v>0.66</v>
+        <v>0.97</v>
       </c>
       <c r="N56" t="n">
-        <v>2.94</v>
+        <v>3.68</v>
       </c>
       <c r="O56" t="n">
         <v>2.66</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>8.33</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45014</v>
+        <v>45016</v>
       </c>
       <c r="H57" t="n">
-        <v>91.55</v>
+        <v>97.55</v>
       </c>
       <c r="I57" t="n">
         <v>97.54990329298137</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="K57" t="n">
-        <v>7.94</v>
+        <v>1.91</v>
       </c>
       <c r="L57" t="n">
         <v>4.58</v>
       </c>
       <c r="M57" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="N57" t="n">
         <v>6.75</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>9.42</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45180</v>
+        <v>45181</v>
       </c>
       <c r="H58" t="n">
-        <v>144.7</v>
+        <v>134.15</v>
       </c>
       <c r="I58" t="n">
         <v>134.9102234125826</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K58" t="n">
-        <v>48.33</v>
+        <v>37.52</v>
       </c>
       <c r="L58" t="n">
         <v>3.38</v>
@@ -3747,7 +4442,7 @@
         <v>1.6</v>
       </c>
       <c r="N58" t="n">
-        <v>3.91</v>
+        <v>7.29</v>
       </c>
       <c r="O58" t="n">
         <v>6.55</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>13.19</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="H59" t="n">
-        <v>138.05</v>
+        <v>140.4</v>
       </c>
       <c r="I59" t="n">
         <v>138.6030106210833</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.91</v>
+        <v>-4.66</v>
       </c>
       <c r="L59" t="n">
         <v>8.09</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.03</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="H60" t="n">
-        <v>180.65</v>
+        <v>174.65</v>
       </c>
       <c r="I60" t="n">
         <v>177.6568514041939</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K60" t="n">
-        <v>28.67</v>
+        <v>24.39</v>
       </c>
       <c r="L60" t="n">
         <v>2.39</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>12.62</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="H61" t="n">
-        <v>188.7</v>
+        <v>194.75</v>
       </c>
       <c r="I61" t="n">
         <v>192.3536025334576</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.039999999999999</v>
+        <v>-11.51</v>
       </c>
       <c r="L61" t="n">
-        <v>10.25</v>
+        <v>12.22</v>
       </c>
       <c r="M61" t="n">
         <v>1.64</v>
       </c>
       <c r="N61" t="n">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="O61" t="n">
         <v>-3.32</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>10.11</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H62" t="n">
-        <v>204.25</v>
+        <v>190.3</v>
       </c>
       <c r="I62" t="n">
         <v>197.0813646896506</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K62" t="n">
-        <v>4.88</v>
+        <v>-2.28</v>
       </c>
       <c r="L62" t="n">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="M62" t="n">
         <v>0.73</v>
       </c>
       <c r="N62" t="n">
-        <v>3.9</v>
+        <v>6.83</v>
       </c>
       <c r="O62" t="n">
         <v>3.21</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>15.05</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H63" t="n">
-        <v>201.5</v>
+        <v>211.1</v>
       </c>
       <c r="I63" t="n">
         <v>209.2212694936707</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.89</v>
+        <v>-10.93</v>
       </c>
       <c r="L63" t="n">
-        <v>8.039999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="M63" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="N63" t="n">
         <v>5.01</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>12.01</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H64" t="n">
-        <v>318.65</v>
+        <v>255.55</v>
       </c>
       <c r="I64" t="n">
         <v>279.1531031935328</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K64" t="n">
-        <v>50.95</v>
+        <v>21.06</v>
       </c>
       <c r="L64" t="n">
         <v>3.48</v>
       </c>
       <c r="M64" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="N64" t="n">
-        <v>2.33</v>
+        <v>19.8</v>
       </c>
       <c r="O64" t="n">
         <v>4.76</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>29.49</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45457</v>
+        <v>45461</v>
       </c>
       <c r="H65" t="n">
-        <v>309.6</v>
+        <v>318.25</v>
       </c>
       <c r="I65" t="n">
         <v>311.4894864132384</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K65" t="n">
-        <v>-21.15</v>
+        <v>-24.54</v>
       </c>
       <c r="L65" t="n">
-        <v>22.09</v>
+        <v>25.61</v>
       </c>
       <c r="M65" t="n">
         <v>3.5</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>15.58</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H66" t="n">
-        <v>312.3</v>
+        <v>301.45</v>
       </c>
       <c r="I66" t="n">
         <v>303.9075024725899</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.87</v>
+        <v>-5.28</v>
       </c>
       <c r="L66" t="n">
-        <v>6.58</v>
+        <v>11.67</v>
       </c>
       <c r="M66" t="n">
         <v>1.16</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>12.81</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="H67" t="n">
-        <v>286.35</v>
+        <v>301.85</v>
       </c>
       <c r="I67" t="n">
         <v>292.8191611310426</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K67" t="n">
-        <v>5.01</v>
+        <v>-0.13</v>
       </c>
       <c r="L67" t="n">
         <v>8.33</v>
@@ -4260,7 +5063,7 @@
         <v>2.87</v>
       </c>
       <c r="N67" t="n">
-        <v>5.04</v>
+        <v>5.41</v>
       </c>
       <c r="O67" t="n">
         <v>-3.47</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.84</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H68" t="n">
-        <v>298.5</v>
+        <v>290.85</v>
       </c>
       <c r="I68" t="n">
         <v>296.8279955040708</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.11</v>
+        <v>-3.64</v>
       </c>
       <c r="L68" t="n">
         <v>10.47</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H69" t="n">
-        <v>278.75</v>
+        <v>292.65</v>
       </c>
       <c r="I69" t="n">
         <v>286.7570628329646</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K69" t="n">
-        <v>4.16</v>
+        <v>-0.62</v>
       </c>
       <c r="L69" t="n">
         <v>3.87</v>
@@ -4374,7 +5201,7 @@
         <v>2.07</v>
       </c>
       <c r="N69" t="n">
-        <v>4.32</v>
+        <v>4.99</v>
       </c>
       <c r="O69" t="n">
         <v>-2.56</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>12.11</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H70" t="n">
-        <v>261.55</v>
+        <v>250.35</v>
       </c>
       <c r="I70" t="n">
         <v>257.2156511947688</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>-10.63</v>
+        <v>-14.45</v>
       </c>
       <c r="L70" t="n">
-        <v>13.21</v>
+        <v>15.19</v>
       </c>
       <c r="M70" t="n">
         <v>1.4</v>
       </c>
       <c r="N70" t="n">
-        <v>3.71</v>
+        <v>4.28</v>
       </c>
       <c r="O70" t="n">
         <v>4.99</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,25 +5318,25 @@
         <v>16.37</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="H71" t="n">
-        <v>272.95</v>
+        <v>276.99</v>
       </c>
       <c r="I71" t="n">
         <v>275.735521259539</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K71" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.64</v>
       </c>
       <c r="L71" t="n">
         <v>12.24</v>
       </c>
       <c r="M71" t="n">
-        <v>0.51</v>
+        <v>1.04</v>
       </c>
       <c r="N71" t="n">
         <v>4.52</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,25 +5387,25 @@
         <v>10.98</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H72" t="n">
-        <v>280</v>
+        <v>272.1</v>
       </c>
       <c r="I72" t="n">
         <v>278.7249939743439</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K72" t="n">
-        <v>1.09</v>
+        <v>-1.77</v>
       </c>
       <c r="L72" t="n">
-        <v>2.87</v>
+        <v>7.51</v>
       </c>
       <c r="M72" t="n">
-        <v>0.85</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N72" t="n">
         <v>3.29</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,22 +5456,22 @@
         <v>9.41</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H73" t="n">
-        <v>295.15</v>
+        <v>299.95</v>
       </c>
       <c r="I73" t="n">
         <v>297.7094615580897</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K73" t="n">
-        <v>-8.470000000000001</v>
+        <v>-10.24</v>
       </c>
       <c r="L73" t="n">
-        <v>9</v>
+        <v>10.84</v>
       </c>
       <c r="M73" t="n">
         <v>3.8</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>9.48</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45855</v>
+        <v>45856</v>
       </c>
       <c r="H74" t="n">
-        <v>404.2</v>
+        <v>394.75</v>
       </c>
       <c r="I74" t="n">
         <v>400.2531288699496</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K74" t="n">
-        <v>34.76</v>
+        <v>31.61</v>
       </c>
       <c r="L74" t="n">
         <v>2.08</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>7.82</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="H75" t="n">
-        <v>371.95</v>
+        <v>388.05</v>
       </c>
       <c r="I75" t="n">
         <v>387.7580778145994</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K75" t="n">
-        <v>5.78</v>
+        <v>1.7</v>
       </c>
       <c r="L75" t="n">
         <v>3.09</v>
@@ -4716,7 +5615,7 @@
         <v>1.38</v>
       </c>
       <c r="N75" t="n">
-        <v>3.27</v>
+        <v>4.33</v>
       </c>
       <c r="O75" t="n">
         <v>-2.34</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>7.87</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="H76" t="n">
-        <v>406.9</v>
+        <v>386.4</v>
       </c>
       <c r="I76" t="n">
         <v>400.7105949672682</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K76" t="n">
-        <v>4.86</v>
+        <v>-0.43</v>
       </c>
       <c r="L76" t="n">
         <v>3.87</v>
@@ -4773,7 +5684,7 @@
         <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>3.01</v>
+        <v>5.04</v>
       </c>
       <c r="O76" t="n">
         <v>4.33</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="77">
@@ -4809,28 +5732,28 @@
         <v>9.67</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H77" t="n">
-        <v>403.15</v>
+        <v>413.8</v>
       </c>
       <c r="I77" t="n">
         <v>405.6197603905971</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K77" t="n">
-        <v>-4.33</v>
+        <v>-7.09</v>
       </c>
       <c r="L77" t="n">
-        <v>5.47</v>
+        <v>8.33</v>
       </c>
       <c r="M77" t="n">
         <v>0.75</v>
       </c>
       <c r="N77" t="n">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="O77" t="n">
         <v>-5.04</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>6.94</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="H78" t="n">
-        <v>430.8</v>
+        <v>426.1</v>
       </c>
       <c r="I78" t="n">
         <v>427.8745700710816</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K78" t="n">
-        <v>4.11</v>
+        <v>2.97</v>
       </c>
       <c r="L78" t="n">
         <v>4.06</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>10.85</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H79" t="n">
-        <v>441.55</v>
+        <v>447.65</v>
       </c>
       <c r="I79" t="n">
         <v>446.3997336827097</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K79" t="n">
-        <v>-3.63</v>
+        <v>-5.06</v>
       </c>
       <c r="L79" t="n">
-        <v>5.01</v>
+        <v>5.42</v>
       </c>
       <c r="M79" t="n">
         <v>3.58</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,28 +5939,28 @@
         <v>8.68</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="H80" t="n">
-        <v>431.95</v>
+        <v>416.5</v>
       </c>
       <c r="I80" t="n">
         <v>425.0430863669749</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K80" t="n">
-        <v>-3.51</v>
+        <v>-6.96</v>
       </c>
       <c r="L80" t="n">
-        <v>5.17</v>
+        <v>7.18</v>
       </c>
       <c r="M80" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="N80" t="n">
-        <v>1.99</v>
+        <v>3.58</v>
       </c>
       <c r="O80" t="n">
         <v>1.38</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>9.18</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="H81" t="n">
-        <v>426.9</v>
+        <v>431.5</v>
       </c>
       <c r="I81" t="n">
         <v>431.3279027561941</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.5</v>
+        <v>-3.6</v>
       </c>
       <c r="L81" t="n">
         <v>4.48</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>6.47</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="H82" t="n">
-        <v>407.15</v>
+        <v>389</v>
       </c>
       <c r="I82" t="n">
         <v>403.5934757132109</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K82" t="n">
-        <v>-5.64</v>
+        <v>-9.85</v>
       </c>
       <c r="L82" t="n">
-        <v>7.16</v>
+        <v>10.08</v>
       </c>
       <c r="M82" t="n">
         <v>0.7</v>
       </c>
       <c r="N82" t="n">
-        <v>2.76</v>
+        <v>4.46</v>
       </c>
       <c r="O82" t="n">
         <v>1.08</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,22 +6146,22 @@
         <v>8.01</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="H83" t="n">
-        <v>405.7</v>
+        <v>410.5</v>
       </c>
       <c r="I83" t="n">
         <v>407.6310035986014</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K83" t="n">
-        <v>-4.29</v>
+        <v>-5.53</v>
       </c>
       <c r="L83" t="n">
-        <v>4.58</v>
+        <v>5.91</v>
       </c>
       <c r="M83" t="n">
         <v>0.55</v>
@@ -5181,7 +6176,19 @@
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S83" t="b">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>1</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -5208,28 +6215,28 @@
         <v>5.95</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H84" t="n">
-        <v>404.35</v>
+        <v>382.9</v>
       </c>
       <c r="I84" t="n">
         <v>394.1001732704089</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K84" t="n">
-        <v>-1.5</v>
+        <v>-6.72</v>
       </c>
       <c r="L84" t="n">
-        <v>2.74</v>
+        <v>6.72</v>
       </c>
       <c r="M84" t="n">
         <v>0.9</v>
       </c>
       <c r="N84" t="n">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="O84" t="n">
         <v>1.18</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5289,6 +6308,14 @@
       <c r="Q85" t="n">
         <v>30</v>
       </c>
+      <c r="R85" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10247,7 +11274,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="6">
@@ -10257,7 +11284,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -10267,7 +11294,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8">
@@ -10277,7 +11304,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -10287,7 +11314,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -10297,7 +11324,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="11">
@@ -10307,7 +11334,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -10317,7 +11344,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -10327,7 +11354,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="14">
@@ -10337,7 +11364,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="15">
@@ -10347,7 +11374,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.23</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="16">
@@ -10357,7 +11384,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.53</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="17">
@@ -10367,7 +11394,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>50.95</v>
+        <v>38.29</v>
       </c>
     </row>
     <row r="18">
@@ -10377,7 +11404,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.4</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="19">
@@ -10387,7 +11414,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.66</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -10397,7 +11424,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.47</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="21">
@@ -10407,7 +11434,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.09</v>
+        <v>25.61</v>
       </c>
     </row>
     <row r="22">
@@ -10417,7 +11444,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -10427,7 +11454,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
@@ -10437,7 +11464,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="25">
@@ -10457,7 +11484,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="27">
@@ -10467,7 +11494,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.47</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="28">
@@ -10477,7 +11504,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
